--- a/Design/config/ArmsConfig.xlsx
+++ b/Design/config/ArmsConfig.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="62">
   <si>
     <t>序列</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -143,6 +143,129 @@
   </si>
   <si>
     <t>士</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>移动速度</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击距离</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>导弹速度</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>导弹高度</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MoveSpeed</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Range</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>MissileSpeed</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MissileHight</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>float</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>cs</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>cs</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>hit</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>HitEffect</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>cs</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SwordHitYellowCritical</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>BulletExplosionBlue</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>FanExplosion</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>shan</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>扇</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GasExplosionFire</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>mou</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>谋</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GasShootFire</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>pao</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>炮</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>che</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>车</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SwordHitGreenCritical</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -150,7 +273,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -178,8 +301,23 @@
       <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -195,6 +333,30 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0070C0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -237,7 +399,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" textRotation="255" wrapText="1"/>
@@ -251,6 +413,20 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" textRotation="255" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -531,16 +707,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.5" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="9.5" customWidth="1"/>
     <col min="4" max="4" width="13.125" customWidth="1"/>
     <col min="5" max="5" width="14.5" customWidth="1"/>
+    <col min="8" max="8" width="22.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="57" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -550,14 +727,29 @@
       <c r="C1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="I1" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="J1" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -567,14 +759,29 @@
       <c r="C2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="I2" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="J2" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>7</v>
       </c>
@@ -584,14 +791,29 @@
       <c r="C3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="J3" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
@@ -601,14 +823,29 @@
       <c r="C4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="I4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="J4" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="3">
         <v>101</v>
       </c>
@@ -618,81 +855,232 @@
       <c r="C5" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="3">
+        <v>10</v>
+      </c>
+      <c r="E5" s="3">
+        <v>17</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="I5" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="J5" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="3">
+        <v>102</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D6" s="3">
+        <v>10</v>
+      </c>
+      <c r="E6" s="3">
+        <v>17</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="I6" s="3"/>
+      <c r="J6" s="3"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A7" s="3">
         <v>201</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C7" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D7" s="3">
+        <v>10</v>
+      </c>
+      <c r="E7" s="3">
+        <v>40</v>
+      </c>
+      <c r="F7" s="3">
+        <v>40</v>
+      </c>
+      <c r="G7" s="3">
+        <v>5</v>
+      </c>
+      <c r="H7" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="I7" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="J7" s="3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A7" s="3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A8" s="3">
+        <v>202</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D8" s="3">
+        <v>10</v>
+      </c>
+      <c r="E8" s="3">
+        <v>17</v>
+      </c>
+      <c r="H8" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A9" s="3">
         <v>601</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B9" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C9" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E7" s="3" t="s">
+      <c r="D9" s="3">
+        <v>10</v>
+      </c>
+      <c r="E9" s="3">
+        <v>17</v>
+      </c>
+      <c r="H9" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="J9" s="3"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A10" s="3">
+        <v>602</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" s="3">
+        <v>10</v>
+      </c>
+      <c r="E10" s="3">
+        <v>17</v>
+      </c>
+      <c r="H10" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J10" s="3"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A11" s="3">
+        <v>603</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D11" s="3">
+        <v>10</v>
+      </c>
+      <c r="E11" s="3">
+        <v>40</v>
+      </c>
+      <c r="F11" s="3">
         <v>30</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A8" s="3">
-        <v>602</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E8" s="3"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A9" s="3">
-        <v>603</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E9" s="3"/>
+      <c r="G11" s="3">
+        <v>3</v>
+      </c>
+      <c r="H11" s="10" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A12" s="3">
+        <v>701</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D12" s="3">
+        <v>10</v>
+      </c>
+      <c r="E12" s="3">
+        <v>40</v>
+      </c>
+      <c r="F12" s="3">
+        <v>30</v>
+      </c>
+      <c r="G12" s="3">
+        <v>3</v>
+      </c>
+      <c r="H12" s="10" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A13" s="3">
+        <v>702</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D13" s="3">
+        <v>7</v>
+      </c>
+      <c r="E13" s="3">
+        <v>50</v>
+      </c>
+      <c r="F13">
+        <v>26</v>
+      </c>
+      <c r="G13" s="3">
+        <v>8</v>
+      </c>
+      <c r="H13" s="10" t="s">
+        <v>56</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A4:C4">
-    <sortState ref="A5:D12">
-      <sortCondition ref="A4:A5"/>
+    <sortState ref="A5:C12">
+      <sortCondition ref="A4"/>
     </sortState>
   </autoFilter>
   <sortState ref="A5:Q43">

--- a/Design/config/ArmsConfig.xlsx
+++ b/Design/config/ArmsConfig.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="72">
   <si>
     <t>序列</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -266,6 +266,46 @@
   </si>
   <si>
     <t>SwordHitGreenCritical</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>模型</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Model</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>cs</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SodStick</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SodBow</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>多少个士兵显示一个模型</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>cs</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ModelCountFactor</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -707,7 +747,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.5" bestFit="1" customWidth="1"/>
@@ -715,9 +755,10 @@
     <col min="4" max="4" width="13.125" customWidth="1"/>
     <col min="5" max="5" width="14.5" customWidth="1"/>
     <col min="8" max="8" width="22.25" customWidth="1"/>
+    <col min="9" max="10" width="10.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" ht="57" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -742,14 +783,20 @@
       <c r="H1" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="K1" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="L1" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -774,14 +821,20 @@
       <c r="H2" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="J2" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="K2" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="L2" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>7</v>
       </c>
@@ -806,14 +859,20 @@
       <c r="H3" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="J3" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="K3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="L3" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
@@ -838,14 +897,20 @@
       <c r="H4" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="I4" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="J4" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="K4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="L4" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="3">
         <v>101</v>
       </c>
@@ -864,14 +929,20 @@
       <c r="H5" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="I5" s="3" t="s">
+      <c r="I5" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="J5" s="9">
+        <v>40</v>
+      </c>
+      <c r="K5" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="J5" s="3" t="s">
+      <c r="L5" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" s="3">
         <v>102</v>
       </c>
@@ -890,10 +961,16 @@
       <c r="H6" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="I6" s="3"/>
-      <c r="J6" s="3"/>
+      <c r="I6" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="J6" s="9">
+        <v>40</v>
+      </c>
+      <c r="K6" s="3"/>
+      <c r="L6" s="3"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="3">
         <v>201</v>
       </c>
@@ -918,14 +995,20 @@
       <c r="H7" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="I7" s="3" t="s">
+      <c r="I7" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="J7" s="9">
+        <v>40</v>
+      </c>
+      <c r="K7" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="J7" s="3" t="s">
+      <c r="L7" s="3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="3">
         <v>202</v>
       </c>
@@ -944,14 +1027,20 @@
       <c r="H8" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="I8" s="3" t="s">
+      <c r="I8" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="J8" s="9">
+        <v>40</v>
+      </c>
+      <c r="K8" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="J8" s="3" t="s">
+      <c r="L8" s="3" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" s="3">
         <v>601</v>
       </c>
@@ -970,12 +1059,18 @@
       <c r="H9" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="I9" s="3" t="s">
+      <c r="I9" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="J9" s="9">
+        <v>40</v>
+      </c>
+      <c r="K9" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="J9" s="3"/>
+      <c r="L9" s="3"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" s="3">
         <v>602</v>
       </c>
@@ -994,12 +1089,18 @@
       <c r="H10" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="I10" s="3" t="s">
+      <c r="I10" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="J10" s="9">
+        <v>40</v>
+      </c>
+      <c r="K10" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="J10" s="3"/>
+      <c r="L10" s="3"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" s="3">
         <v>603</v>
       </c>
@@ -1024,8 +1125,14 @@
       <c r="H11" s="10" t="s">
         <v>50</v>
       </c>
+      <c r="I11" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="J11" s="9">
+        <v>40</v>
+      </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
         <v>701</v>
       </c>
@@ -1050,8 +1157,14 @@
       <c r="H12" s="10" t="s">
         <v>53</v>
       </c>
+      <c r="I12" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="J12" s="9">
+        <v>40</v>
+      </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" s="3">
         <v>702</v>
       </c>
@@ -1067,7 +1180,7 @@
       <c r="E13" s="3">
         <v>50</v>
       </c>
-      <c r="F13">
+      <c r="F13" s="3">
         <v>26</v>
       </c>
       <c r="G13" s="3">
@@ -1075,6 +1188,12 @@
       </c>
       <c r="H13" s="10" t="s">
         <v>56</v>
+      </c>
+      <c r="I13" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="J13" s="9">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
